--- a/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
+++ b/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
@@ -59,10 +59,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -478,6 +481,43 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="80" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>宗田雅史</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>税理士（開業6年）→いい塾（経営者勉強会）に変更中</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>税理士</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>不明（関西圏推測）</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>パチスロ話で即打ち解け。BNIルール案内後、由香さんのエンパス体質・タマラ・保健室の成り立ちを紹介。宗田さんの背景（姉との比較・やんちゃ・税理士道・初担当客の自殺が使命感の原点）も深く話した。チャクラワーク体験（第三チャクラが黒く大きい→白く浄化→体が楽になった）。亡くなったクライアントからの伝言を受け取り涙ぐむ。利き脳＝左左タイプ（理論・社会のために力が湧く）。タマラセッション申込み意向あり。リアライズ全体への利き脳ワーク提案に乗り気。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
+++ b/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -475,7 +475,22 @@
           <t>住んでいる地域</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>利き脳</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>VAK</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>紹介してほしい人（求めるリファーラル）</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>要約</t>
         </is>
@@ -512,7 +527,17 @@
           <t>不明（関西圏推測）</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>誠</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>パチスロ話で即打ち解け。BNIルール案内後、由香さんのエンパス体質・タマラ・保健室の成り立ちを紹介。宗田さんの背景（姉との比較・やんちゃ・税理士道・初担当客の自殺が使命感の原点）も深く話した。チャクラワーク体験（第三チャクラが黒く大きい→白く浄化→体が楽になった）。亡くなったクライアントからの伝言を受け取り涙ぐむ。利き脳＝左左タイプ（理論・社会のために力が湧く）。タマラセッション申込み意向あり。リアライズ全体への利き脳ワーク提案に乗り気。</t>
         </is>

--- a/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
+++ b/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -543,6 +543,58 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>富吉亨</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>日用品アドバイザー（BlueBird）</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>生活関連サービス</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>大阪</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>コネクトの活用知識がREALIZEで突出。誠実・丁寧なスタンス。健康関係のお仕事。「妥協しない」姿勢。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>大阪府下の出産予定ご夫婦</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>コネクトパスポートプログラムを担当してもらい住所公開リスクを指摘・修正。コネクト勉強会共催の可能性あり。7月BODで対面予定。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
+++ b/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -595,6 +595,286 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上田</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>不明（REALIZE）</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>介護の販売の人</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>由香さんから介護の販売の方を紹介したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>杉さん</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>沼さん・和田さん</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>由香さんから沼さん・和田さんを紹介したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>すざきさん</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ゆっちぃ（AI活用・Claude Code）の事を相談したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>平沢さん</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不明（トラック15台以上保有）</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>物流・輸送</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>トラック15台以上持っている人・青木さん</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>由香さんからトラック15台以上の方と青木さんを紹介したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>山根さん</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>気になっている・1to1希望</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>M&amp;Aの人</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>不明（M&amp;A関連）</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>M&amp;A</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>しょうがおじさん</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>由香さんからしょうがおじさんをご紹介したい</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>廣瀬</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026年7月24日 9〜12時 研修受ける予定</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>【要確認】不明</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>自衛隊・消防士</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>自衛隊・消防士を紹介してほしいと言っていたメンバーがいるが氏名不明。要確認。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
+++ b/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -616,10 +616,6 @@
           <t>不明（REALIZE）</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>介護の販売の人</t>
@@ -652,10 +648,6 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>沼さん・和田さん</t>
@@ -688,11 +680,6 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>ゆっちぃ（AI活用・Claude Code）の事を相談したい</t>
@@ -725,9 +712,6 @@
           <t>物流・輸送</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>トラック15台以上持っている人・青木さん</t>
@@ -760,11 +744,6 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>気になっている・1to1希望</t>
@@ -797,9 +776,6 @@
           <t>M&amp;A</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>しょうがおじさん</t>
@@ -832,11 +808,6 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2026年7月24日 9〜12時 研修受ける予定</t>
@@ -859,11 +830,6 @@
           <t>【要確認】不明</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>自衛隊・消防士</t>
@@ -872,6 +838,42 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>自衛隊・消防士を紹介してほしいと言っていたメンバーがいるが氏名不明。要確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>畑さん</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>大関謙吾（けんけん）</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ペット共生リフォーム関連で大関さんと合いそう。由香さんから紹介したい。</t>
         </is>
       </c>
     </row>

--- a/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
+++ b/20_Projects/BNI_REALIZE/121記録/BNI_121記録.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -862,10 +862,6 @@
           <t>不明</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>大関謙吾（けんけん）</t>
@@ -874,6 +870,58 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>ペット共生リフォーム関連で大関さんと合いそう。由香さんから紹介したい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BNI REALIZE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>永廣勇資</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>社会保険労務士（ながひろ社労士事務所・大阪市西区）</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>社会保険労務士</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>大阪市西区</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>不明（INFP）</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ハラスメント問題を抱える中小企業の社長・総務担当者／社員の話を聞ける相談窓口が必要な企業</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>脱ハラスメント専門の社労士。大阪拠点・全国リモート対応。奥さんと子のハラスメント被害経験から使命感。ハラスメントの線引き教育・経営陣バージョンアップが得意。単発相談1時間10,000円も可。企業のオンライン保健室との協業合意：由香さんが感情ハブ→法的・制度的問題は永廣さんへリファー。障害年金支援も兼務。7月24日リアルBODで対面予定。</t>
         </is>
       </c>
     </row>
